--- a/endpoint-inventory.xlsx
+++ b/endpoint-inventory.xlsx
@@ -4,34 +4,34 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Endpoints" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="Endpoint Inventory" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="49">
   <si>
     <t>Endpoint</t>
   </si>
   <si>
-    <t>HTTP method</t>
-  </si>
-  <si>
-    <t>Authentication required</t>
-  </si>
-  <si>
-    <t>Expected role</t>
-  </si>
-  <si>
-    <t>Request body</t>
-  </si>
-  <si>
-    <t>Expected status code</t>
-  </si>
-  <si>
-    <t>Controller/source file</t>
+    <t>Method</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Parameter</t>
+  </si>
+  <si>
+    <t>Required Role</t>
+  </si>
+  <si>
+    <t>Authenticated?</t>
+  </si>
+  <si>
+    <t>Rate Limited?</t>
   </si>
   <si>
     <t>/api/auth/login</t>
@@ -40,31 +40,28 @@
     <t>POST</t>
   </si>
   <si>
+    <t>User authentication &amp; JWT issue</t>
+  </si>
+  <si>
+    <t>email, password</t>
+  </si>
+  <si>
+    <t>Any</t>
+  </si>
+  <si>
     <t>No</t>
   </si>
   <si>
-    <t>Any registered</t>
-  </si>
-  <si>
-    <t>{"email": "string"}</t>
-  </si>
-  <si>
-    <t>200 (Success), 404 (Not Found), 500 (Error)</t>
-  </si>
-  <si>
-    <t>backend/server.js</t>
+    <t>Yes (20/15min)</t>
   </si>
   <si>
     <t>/api/auth/register</t>
   </si>
   <si>
-    <t>Guest user</t>
-  </si>
-  <si>
-    <t>{"name": "string", "email": "string", "role": "student|admin|faculty", "department": "string", "rollNumber": "string", "phone": "string"}</t>
-  </si>
-  <si>
-    <t>201 (Created), 400 (Bad Request), 500 (Error)</t>
+    <t>Create new user account</t>
+  </si>
+  <si>
+    <t>name, email, password, role, department, rollNumber, phone</t>
   </si>
   <si>
     <t>/api/auth/profile</t>
@@ -73,76 +70,94 @@
     <t>PUT</t>
   </si>
   <si>
-    <t>Authenticated</t>
-  </si>
-  <si>
-    <t>{"userId": "string", "name": "string", "department": "string", "year": "string", "rollNumber": "string", "phone": "string"}</t>
-  </si>
-  <si>
-    <t>200 (Success), 400 (Missing userId), 404 (Not Found), 500 (Error)</t>
-  </si>
-  <si>
-    <t>/api/users</t>
+    <t>Update profile properties</t>
+  </si>
+  <si>
+    <t>userId, phone, department</t>
+  </si>
+  <si>
+    <t>Authenticated User</t>
+  </si>
+  <si>
+    <t>Yes (JWT)</t>
+  </si>
+  <si>
+    <t>Yes (200/15min)</t>
+  </si>
+  <si>
+    <t>/api/events</t>
   </si>
   <si>
     <t>GET</t>
   </si>
   <si>
-    <t>admin</t>
+    <t>Get all event listings</t>
   </si>
   <si>
     <t>None</t>
   </si>
   <si>
-    <t>200 (Success), 500 (Error)</t>
-  </si>
-  <si>
-    <t>/api/events</t>
-  </si>
-  <si>
-    <t>Guest / User</t>
-  </si>
-  <si>
-    <t>admin | faculty</t>
-  </si>
-  <si>
-    <t>{"title": "string", "category": "string", "date": "Date", "endDate": "Date", "venue": "string", "capacity": 0, "price": 0, ...}</t>
-  </si>
-  <si>
-    <t>201 (Created), 500 (Error)</t>
+    <t>Publish new event</t>
+  </si>
+  <si>
+    <t>title, description, category, date, venue, capacity</t>
+  </si>
+  <si>
+    <t>ADMIN, FACULTY</t>
   </si>
   <si>
     <t>/api/events/:id</t>
   </si>
   <si>
-    <t>{"title": "string", ...}</t>
+    <t>Get single event detail</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>Update event metadata</t>
+  </si>
+  <si>
+    <t>id, title, venue, etc.</t>
   </si>
   <si>
     <t>DELETE</t>
   </si>
   <si>
+    <t>Delete event</t>
+  </si>
+  <si>
+    <t>ADMIN</t>
+  </si>
+  <si>
     <t>/api/events/:id/register</t>
   </si>
   <si>
-    <t>student</t>
-  </si>
-  <si>
-    <t>{"userId": "string", "userName": "string", "userEmail": "string", "userPhone": "string", "department": "string", "paymentScreenshot": "string"}</t>
-  </si>
-  <si>
-    <t>200 (Success), 400 (Bad Request), 404 (Not Found), 500 (Error)</t>
+    <t>Register user for event</t>
+  </si>
+  <si>
+    <t>id, name, email, roll</t>
   </si>
   <si>
     <t>/api/events/:id/register/:userId</t>
   </si>
   <si>
-    <t>student | admin</t>
+    <t>Cancel registration</t>
+  </si>
+  <si>
+    <t>id, userId</t>
   </si>
   <si>
     <t>/api/events/:id/attendance</t>
   </si>
   <si>
-    <t>{"userId": "string"}</t>
+    <t>Mark attendee attendance</t>
+  </si>
+  <si>
+    <t>/api/health</t>
+  </si>
+  <si>
+    <t>Health check &amp; security header test</t>
   </si>
 </sst>
 </file>
@@ -171,11 +186,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="2E8FE8"/>
+        <fgColor rgb="1F497D"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -183,36 +198,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="E0E0E0"/>
-      </left>
-      <right style="thin">
-        <color rgb="E0E0E0"/>
-      </right>
-      <top style="thin">
-        <color rgb="E0E0E0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="E0E0E0"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -555,16 +547,15 @@
   <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="35" customWidth="1"/>
+    <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="45" customWidth="1"/>
-    <col min="6" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="25" customWidth="1"/>
+    <col min="3" max="3" width="45" customWidth="1"/>
+    <col min="4" max="4" width="25" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
+    <col min="6" max="7" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -588,279 +579,279 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="A3" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="C3" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="D3" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="B4" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" t="s">
         <v>22</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>13</v>
+      <c r="G4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" s="3" t="s">
+      <c r="A5" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="3" t="s">
+      <c r="B5" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="C5" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="D5" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>13</v>
+      <c r="E5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="A6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" s="3" t="s">
+      <c r="E6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="3" t="s">
+      <c r="E13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>13</v>
+      <c r="G13" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
